--- a/2026_WorldCup_Player.xlsx
+++ b/2026_WorldCup_Player.xlsx
@@ -5,16 +5,22 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_sample_python\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24994D08-01C4-4AF5-A334-6C0ED5B3B284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF1CC41-8F94-4857-BB26-7AD69B4A9E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32340" yWindow="1080" windowWidth="20010" windowHeight="11220" xr2:uid="{D39A83F6-04F0-4526-9464-7BBE9DA55337}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D39A83F6-04F0-4526-9464-7BBE9DA55337}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="teams" sheetId="2" r:id="rId1"/>
+    <sheet name="teams_2022" sheetId="4" r:id="rId2"/>
+    <sheet name="team_korea" sheetId="1" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">teams!$A$1:$D$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">teams_2022!$A$1:$D$49</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="116">
   <si>
     <t>선수</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -237,6 +243,265 @@
   </si>
   <si>
     <t>조현우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐나다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>멕시코</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일본</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뉴질랜드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이란</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아르헨티나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우즈베키스탄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대한민국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요르단</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에콰도르</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>브라질</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우루과이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콜롬비아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파라과이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모로코</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>튀니지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이집트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알제리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카보베르데</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남아프리카공화국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카타르</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잉글랜드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사우디아라비아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코트디부아르</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세네갈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프랑스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크로아티아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포르투갈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노르웨이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>독일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네덜란드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>벨기에</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오스트리아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스위스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스페인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스코틀랜드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파나마</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀴라소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이티</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스웨덴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>튀르키예</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체코</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스나아헤르체고비나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콩고민주공화국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이라크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아프리카</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>북중미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아시아</t>
+  </si>
+  <si>
+    <t>아시아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오세아니아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유럽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대륙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국가명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>피파랭킹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진출횟수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카메룬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코스타리카</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>덴마크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세르비아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폴란드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>웨일스</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -244,7 +509,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,6 +522,14 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -283,8 +556,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -600,6 +876,1191 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A226A8C-CB8F-4985-9DC5-E26E03AF9238}">
+  <dimension ref="A1:D49"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2">
+        <v>30</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3">
+        <v>15</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5">
+        <v>18</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6">
+        <v>85</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7">
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9">
+        <v>50</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10">
+        <v>25</v>
+      </c>
+      <c r="D10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11">
+        <v>63</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12">
+        <v>27</v>
+      </c>
+      <c r="D12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13">
+        <v>23</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15">
+        <v>17</v>
+      </c>
+      <c r="D15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16">
+        <v>13</v>
+      </c>
+      <c r="D16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17">
+        <v>40</v>
+      </c>
+      <c r="D17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18">
+        <v>8</v>
+      </c>
+      <c r="D18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19">
+        <v>44</v>
+      </c>
+      <c r="D19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20">
+        <v>29</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21">
+        <v>28</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22">
+        <v>74</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23">
+        <v>69</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24">
+        <v>60</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25">
+        <v>55</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27">
+        <v>61</v>
+      </c>
+      <c r="D27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28">
+        <v>34</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29">
+        <v>14</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32">
+        <v>5</v>
+      </c>
+      <c r="D32">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33">
+        <v>31</v>
+      </c>
+      <c r="D33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34">
+        <v>10</v>
+      </c>
+      <c r="D34">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35">
+        <v>7</v>
+      </c>
+      <c r="D35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36">
+        <v>9</v>
+      </c>
+      <c r="D36">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37">
+        <v>24</v>
+      </c>
+      <c r="D37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38">
+        <v>19</v>
+      </c>
+      <c r="D38">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40">
+        <v>43</v>
+      </c>
+      <c r="D40">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41">
+        <v>33</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42">
+        <v>82</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43">
+        <v>83</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44">
+        <v>38</v>
+      </c>
+      <c r="D44">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45">
+        <v>22</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" t="s">
+        <v>105</v>
+      </c>
+      <c r="C46">
+        <v>41</v>
+      </c>
+      <c r="D46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47">
+        <v>65</v>
+      </c>
+      <c r="D47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48">
+        <v>46</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49">
+        <v>57</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D49" xr:uid="{1A226A8C-CB8F-4985-9DC5-E26E03AF9238}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CBD1A69-F0C6-48C3-8E14-A092A9E5FFCE}">
+  <dimension ref="A1:D49"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2">
+        <v>51</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3">
+        <v>21</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4">
+        <v>29</v>
+      </c>
+      <c r="D4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5">
+        <v>49</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9">
+        <v>37</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10">
+        <v>60</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11">
+        <v>24</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12">
+        <v>35</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13">
+        <v>38</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15">
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16">
+        <v>31</v>
+      </c>
+      <c r="D16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19">
+        <v>13</v>
+      </c>
+      <c r="D19">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20">
+        <v>46</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21">
+        <v>12</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25">
+        <v>25</v>
+      </c>
+      <c r="D25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26">
+        <v>7</v>
+      </c>
+      <c r="D26">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27">
+        <v>16</v>
+      </c>
+      <c r="D27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29">
+        <v>14</v>
+      </c>
+      <c r="D29">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30">
+        <v>10</v>
+      </c>
+      <c r="D30">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>114</v>
+      </c>
+      <c r="B31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31">
+        <v>26</v>
+      </c>
+      <c r="D31">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32">
+        <v>8</v>
+      </c>
+      <c r="D32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33">
+        <v>18</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B49" s="1"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D49" xr:uid="{1A226A8C-CB8F-4985-9DC5-E26E03AF9238}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211F14F9-6C28-4944-AA57-3D142371A5AB}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
